--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -790,7 +790,7 @@
         <v>0.03052600000000001</v>
       </c>
       <c r="E16">
-        <v>-4.280000000073114E-05</v>
+        <v>-4.280000000072559E-05</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>0.02636791788961459</v>
       </c>
       <c r="E24">
-        <v>7.333760727235573E-05</v>
+        <v>7.333760727237792E-05</v>
       </c>
       <c r="F24">
         <v>10</v>
